--- a/MinMax/scripts/comparison/accuracy_comparison_table_57_1000_False.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_57_1000_False.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\bagir\Documents\1) Projects\2) AC verification\MinMax\scripts\comparison\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375EC875-5495-43B0-9562-3390CB85D315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -124,8 +118,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,21 +182,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -240,7 +226,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -274,7 +260,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -309,10 +294,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -485,16 +469,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="24.81640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -511,41 +490,41 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1.054969965480268E-3</v>
+        <v>0.001054969965480268</v>
       </c>
       <c r="C2">
-        <v>1.1750835983548311E-4</v>
+        <v>0.0001175083598354831</v>
       </c>
       <c r="D2">
-        <v>1.12441681267228E-4</v>
+        <v>0.000112441681267228</v>
       </c>
       <c r="E2">
-        <v>1.12441681267228E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.000112441681267228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3">
-        <v>1.507208775728941E-2</v>
+        <v>0.01507208775728941</v>
       </c>
       <c r="C3">
-        <v>2.8963531367480751E-3</v>
+        <v>0.002896353136748075</v>
       </c>
       <c r="D3">
-        <v>1.255041104741395E-3</v>
+        <v>0.001255041104741395</v>
       </c>
       <c r="E3">
-        <v>1.255041104741395E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.001255041104741395</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -562,41 +541,41 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>7.9161388566717505E-4</v>
+        <v>0.0007916138856671751</v>
       </c>
       <c r="C5">
-        <v>1.193766584037803E-4</v>
+        <v>0.0001193766584037803</v>
       </c>
       <c r="D5">
-        <v>1.1402300879126411E-4</v>
+        <v>0.0001140230087912641</v>
       </c>
       <c r="E5">
-        <v>1.1402300879126411E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.0001140230087912641</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.35308307409286499</v>
+        <v>0.353083074092865</v>
       </c>
       <c r="C6">
-        <v>1.319265342317522E-3</v>
+        <v>0.001319265342317522</v>
       </c>
       <c r="D6">
-        <v>4.3190197902731597E-4</v>
+        <v>0.000431901979027316</v>
       </c>
       <c r="E6">
-        <v>4.3190197902731597E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.000431901979027316</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -613,24 +592,24 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B8">
-        <v>2.6694926253032999E-16</v>
+        <v>2.6694926253033E-16</v>
       </c>
       <c r="C8">
-        <v>2.6694926253032999E-16</v>
+        <v>2.6694926253033E-16</v>
       </c>
       <c r="D8">
-        <v>2.6694926253032999E-16</v>
+        <v>2.6694926253033E-16</v>
       </c>
       <c r="E8">
-        <v>2.6694926253032999E-16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+        <v>2.6694926253033E-16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -647,7 +626,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -655,166 +634,166 @@
         <v>0.3537909984588623</v>
       </c>
       <c r="C10">
-        <v>1.32113613653928E-3</v>
+        <v>0.00132113613653928</v>
       </c>
       <c r="D10">
-        <v>4.3294025817885989E-4</v>
+        <v>0.0004329402581788599</v>
       </c>
       <c r="E10">
-        <v>4.3294025817885989E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.0004329402581788599</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B11">
-        <v>1.5965755455659581E-17</v>
+        <v>1.596575545565958E-17</v>
       </c>
       <c r="C11">
-        <v>1.5965755455659581E-17</v>
+        <v>1.596575545565958E-17</v>
       </c>
       <c r="D11">
-        <v>1.5965755455659581E-17</v>
+        <v>1.596575545565958E-17</v>
       </c>
       <c r="E11">
-        <v>1.5965755455659581E-17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+        <v>1.596575545565958E-17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>1.031687948852777E-2</v>
+        <v>0.01031687948852777</v>
       </c>
       <c r="C12">
-        <v>3.5287259379401803E-5</v>
+        <v>3.52872593794018E-05</v>
       </c>
       <c r="D12">
-        <v>2.552624391682912E-5</v>
+        <v>2.552624391682912E-05</v>
       </c>
       <c r="E12">
-        <v>2.552624391682912E-5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+        <v>2.552624391682912E-05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B13">
-        <v>8.7708320617675781</v>
+        <v>8.770832061767578</v>
       </c>
       <c r="C13">
-        <v>3.2483071088790887E-2</v>
+        <v>0.03248307108879089</v>
       </c>
       <c r="D13">
-        <v>9.7425151616334915E-3</v>
+        <v>0.009742515161633492</v>
       </c>
       <c r="E13">
-        <v>9.7425151616334915E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.009742515161633492</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B14">
-        <v>7.332904264330864E-3</v>
+        <v>0.007332904264330864</v>
       </c>
       <c r="C14">
-        <v>9.0093252947553992E-4</v>
+        <v>0.0009009325294755399</v>
       </c>
       <c r="D14">
-        <v>5.9446640079841018E-4</v>
+        <v>0.0005944664007984102</v>
       </c>
       <c r="E14">
-        <v>5.9446640079841018E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.0005944664007984102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B15">
-        <v>7.2881910018622884E-3</v>
+        <v>0.007288191001862288</v>
       </c>
       <c r="C15">
-        <v>8.9278933592140675E-4</v>
+        <v>0.0008927893359214067</v>
       </c>
       <c r="D15">
-        <v>5.8657600311562419E-4</v>
+        <v>0.0005865760031156242</v>
       </c>
       <c r="E15">
-        <v>5.8657600311562419E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.0005865760031156242</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.16393749415874481</v>
+        <v>0.1639374941587448</v>
       </c>
       <c r="C16">
-        <v>2.6330934837460521E-2</v>
+        <v>0.02633093483746052</v>
       </c>
       <c r="D16">
-        <v>8.6899213492870331E-3</v>
+        <v>0.008689921349287033</v>
       </c>
       <c r="E16">
-        <v>8.6899213492870331E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.008689921349287033</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B17">
-        <v>1.7710952088236809E-2</v>
+        <v>0.01771095208823681</v>
       </c>
       <c r="C17">
-        <v>3.2468810677528381E-3</v>
+        <v>0.003246881067752838</v>
       </c>
       <c r="D17">
-        <v>1.2900182045996189E-3</v>
+        <v>0.001290018204599619</v>
       </c>
       <c r="E17">
-        <v>1.2900182045996189E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.001290018204599619</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B18">
-        <v>0.92800480127334595</v>
+        <v>0.9280048012733459</v>
       </c>
       <c r="C18">
-        <v>3.9788451977074146E-3</v>
+        <v>0.003978845197707415</v>
       </c>
       <c r="D18">
-        <v>1.0650062467902901E-3</v>
+        <v>0.00106500624679029</v>
       </c>
       <c r="E18">
-        <v>1.0650062467902901E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.00106500624679029</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B19">
-        <v>0.93316072225570679</v>
+        <v>0.9331607222557068</v>
       </c>
       <c r="C19">
-        <v>3.7228618748486042E-3</v>
+        <v>0.003722861874848604</v>
       </c>
       <c r="D19">
-        <v>1.0255281813442709E-3</v>
+        <v>0.001025528181344271</v>
       </c>
       <c r="E19">
-        <v>1.0255281813442709E-3</v>
+        <v>0.001025528181344271</v>
       </c>
     </row>
   </sheetData>

--- a/MinMax/scripts/comparison/accuracy_comparison_table_57_1000_False.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_57_1000_False.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Pg Vm Projection False</t>
   </si>
@@ -34,85 +34,91 @@
     <t>vr_tot</t>
   </si>
   <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>pd_tot</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>vm_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_r_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
     <t>Iinj_i_tot</t>
   </si>
   <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>vm_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_r_tot</t>
-  </si>
-  <si>
     <t>solve_time</t>
   </si>
   <si>
-    <t>pd_tot</t>
-  </si>
-  <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
+    <t>sample_num</t>
   </si>
   <si>
     <t>qg_tot</t>
   </si>
   <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>30364.74 (26860.10 &gt; 13.54%)</t>
-  </si>
-  <si>
-    <t>1.23s (1.05 s)</t>
-  </si>
-  <si>
-    <t>1.81 (2.45)</t>
-  </si>
-  <si>
-    <t>27078.77 (26860.10 &gt; 0.81%)</t>
-  </si>
-  <si>
-    <t>0.48s (1.05 s)</t>
-  </si>
-  <si>
-    <t>2.34 (2.45)</t>
-  </si>
-  <si>
-    <t>26866.52 (26860.10 &gt; 0.02%)</t>
-  </si>
-  <si>
-    <t>1.08s (1.05 s)</t>
-  </si>
-  <si>
-    <t>2.45 (2.45)</t>
-  </si>
-  <si>
-    <t>0.84s (1.05 s)</t>
+    <t>30471.75 (27040.55 &gt; 12.69%)</t>
+  </si>
+  <si>
+    <t>183.36 (245.00)</t>
+  </si>
+  <si>
+    <t>0.15s (0.18 s)</t>
+  </si>
+  <si>
+    <t>27271.75 (27104.39 &gt; 0.62%)</t>
+  </si>
+  <si>
+    <t>237.05 (245.00)</t>
+  </si>
+  <si>
+    <t>0.14s (0.18 s)</t>
+  </si>
+  <si>
+    <t>27086.55 (27086.60 &gt; 0.00%)</t>
+  </si>
+  <si>
+    <t>245.00 (245.00)</t>
+  </si>
+  <si>
+    <t>0.10s (0.18 s)</t>
+  </si>
+  <si>
+    <t>27016.25 (27016.29 &gt; 0.00%)</t>
+  </si>
+  <si>
+    <t>0.11s (0.18 s)</t>
   </si>
 </sst>
 </file>
@@ -470,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -495,16 +501,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.001054969965480268</v>
+        <v>0.0008223086479119956</v>
       </c>
       <c r="C2">
-        <v>0.0001175083598354831</v>
+        <v>7.763875328237191E-05</v>
       </c>
       <c r="D2">
-        <v>0.000112441681267228</v>
+        <v>7.149902376113459E-05</v>
       </c>
       <c r="E2">
-        <v>0.000112441681267228</v>
+        <v>7.264853775268421E-05</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -512,33 +518,33 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.01507208775728941</v>
+        <v>0.007784114684909582</v>
       </c>
       <c r="C3">
-        <v>0.002896353136748075</v>
+        <v>0.007765873335301876</v>
       </c>
       <c r="D3">
-        <v>0.001255041104741395</v>
+        <v>0.007777412422001362</v>
       </c>
       <c r="E3">
-        <v>0.001255041104741395</v>
+        <v>0.007734283339232206</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
+      <c r="B4">
+        <v>0.2994965612888336</v>
+      </c>
+      <c r="C4">
+        <v>0.2948457002639771</v>
+      </c>
+      <c r="D4">
+        <v>0.2941088974475861</v>
+      </c>
+      <c r="E4">
+        <v>0.2934346497058868</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -546,16 +552,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.0007916138856671751</v>
+        <v>0.939612865447998</v>
       </c>
       <c r="C5">
-        <v>0.0001193766584037803</v>
+        <v>0.01165850553661585</v>
       </c>
       <c r="D5">
-        <v>0.0001140230087912641</v>
+        <v>0.01311658881604671</v>
       </c>
       <c r="E5">
-        <v>0.0001140230087912641</v>
+        <v>0.01332925725728273</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -563,33 +569,33 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.353083074092865</v>
+        <v>0.9275590777397156</v>
       </c>
       <c r="C6">
-        <v>0.001319265342317522</v>
+        <v>0.01068335864692926</v>
       </c>
       <c r="D6">
-        <v>0.000431901979027316</v>
+        <v>0.01241381466388702</v>
       </c>
       <c r="E6">
-        <v>0.000431901979027316</v>
+        <v>0.01264255959540606</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
+      <c r="B7">
+        <v>0.006360871717333794</v>
+      </c>
+      <c r="C7">
+        <v>0.006291237194091082</v>
+      </c>
+      <c r="D7">
+        <v>0.006427791435271502</v>
+      </c>
+      <c r="E7">
+        <v>0.006491480395197868</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -597,33 +603,33 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>2.6694926253033E-16</v>
+        <v>0.0003507673682179302</v>
       </c>
       <c r="C8">
-        <v>2.6694926253033E-16</v>
+        <v>0.0003319226671010256</v>
       </c>
       <c r="D8">
-        <v>2.6694926253033E-16</v>
+        <v>0.0003492638643365353</v>
       </c>
       <c r="E8">
-        <v>2.6694926253033E-16</v>
+        <v>0.000352771021425724</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
+      <c r="B9">
+        <v>0.0105419410392642</v>
+      </c>
+      <c r="C9">
+        <v>9.746655996423215E-05</v>
+      </c>
+      <c r="D9">
+        <v>0.0001299446012126282</v>
+      </c>
+      <c r="E9">
+        <v>0.0001312893291469663</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -631,33 +637,33 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>0.3537909984588623</v>
+        <v>8.853816986083984</v>
       </c>
       <c r="C10">
-        <v>0.00132113613653928</v>
+        <v>0.15057572722435</v>
       </c>
       <c r="D10">
-        <v>0.0004329402581788599</v>
+        <v>0.1571007519960403</v>
       </c>
       <c r="E10">
-        <v>0.0004329402581788599</v>
+        <v>0.1585016399621964</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11">
-        <v>1.596575545565958E-17</v>
-      </c>
-      <c r="C11">
-        <v>1.596575545565958E-17</v>
-      </c>
-      <c r="D11">
-        <v>1.596575545565958E-17</v>
-      </c>
-      <c r="E11">
-        <v>1.596575545565958E-17</v>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -665,16 +671,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.01031687948852777</v>
+        <v>0.0005989582859911025</v>
       </c>
       <c r="C12">
-        <v>3.52872593794018E-05</v>
+        <v>7.205095607787371E-05</v>
       </c>
       <c r="D12">
-        <v>2.552624391682912E-05</v>
+        <v>6.404146552085876E-05</v>
       </c>
       <c r="E12">
-        <v>2.552624391682912E-05</v>
+        <v>6.499428127426654E-05</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -682,16 +688,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>8.770832061767578</v>
+        <v>0.2999360859394073</v>
       </c>
       <c r="C13">
-        <v>0.03248307108879089</v>
+        <v>0.2952981889247894</v>
       </c>
       <c r="D13">
-        <v>0.009742515161633492</v>
+        <v>0.2945624589920044</v>
       </c>
       <c r="E13">
-        <v>0.009742515161633492</v>
+        <v>0.2938857078552246</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -699,33 +705,33 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.007332904264330864</v>
+        <v>0.01944625005125999</v>
       </c>
       <c r="C14">
-        <v>0.0009009325294755399</v>
+        <v>0.00538887782022357</v>
       </c>
       <c r="D14">
-        <v>0.0005944664007984102</v>
+        <v>0.003250016598030925</v>
       </c>
       <c r="E14">
-        <v>0.0005944664007984102</v>
+        <v>0.003282362129539251</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15">
-        <v>0.007288191001862288</v>
-      </c>
-      <c r="C15">
-        <v>0.0008927893359214067</v>
-      </c>
-      <c r="D15">
-        <v>0.0005865760031156242</v>
-      </c>
-      <c r="E15">
-        <v>0.0005865760031156242</v>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -733,16 +739,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.1639374941587448</v>
+        <v>0.007124858908355236</v>
       </c>
       <c r="C16">
-        <v>0.02633093483746052</v>
+        <v>0.007110359612852335</v>
       </c>
       <c r="D16">
-        <v>0.008689921349287033</v>
+        <v>0.007119691930711269</v>
       </c>
       <c r="E16">
-        <v>0.008689921349287033</v>
+        <v>0.007078637834638357</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -750,50 +756,55 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.01771095208823681</v>
+        <v>0.007817907258868217</v>
       </c>
       <c r="C17">
-        <v>0.003246881067752838</v>
+        <v>0.004335019737482071</v>
       </c>
       <c r="D17">
-        <v>0.001290018204599619</v>
+        <v>0.002623818349093199</v>
       </c>
       <c r="E17">
-        <v>0.001290018204599619</v>
+        <v>0.002627004636451602</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18">
-        <v>0.9280048012733459</v>
-      </c>
-      <c r="C18">
-        <v>0.003978845197707415</v>
-      </c>
-      <c r="D18">
-        <v>0.00106500624679029</v>
-      </c>
-      <c r="E18">
-        <v>0.00106500624679029</v>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B19">
-        <v>0.9331607222557068</v>
-      </c>
-      <c r="C19">
-        <v>0.003722861874848604</v>
-      </c>
-      <c r="D19">
-        <v>0.001025528181344271</v>
-      </c>
-      <c r="E19">
-        <v>0.001025528181344271</v>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.1845953762531281</v>
+      </c>
+      <c r="C20">
+        <v>0.05390773341059685</v>
+      </c>
+      <c r="D20">
+        <v>0.03321878984570503</v>
+      </c>
+      <c r="E20">
+        <v>0.03347017988562584</v>
       </c>
     </row>
   </sheetData>
